--- a/Data/ECON_소비자물가지수_KK.xlsx
+++ b/Data/ECON_소비자물가지수_KK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\내 드라이브\Research\SavedData\KorailEconNews\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DataScience\Lecture\특강_20250412_한국지능정보사회진흥원_빅데이터센터\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3E2F4C-A220-4677-B0C0-77B30BD883AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3590DBDD-C191-4721-BBB5-7464442989E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24098" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="데이터" sheetId="1" r:id="rId1"/>
@@ -569,7 +569,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.0000000000_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -579,11 +579,15 @@
       <sz val="10.5"/>
       <color rgb="FF555555"/>
       <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF888282"/>
       <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="8"/>
@@ -659,10 +663,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1000,141 +1004,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC129"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="29" width="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="23.25" customHeight="1">
+    <row r="1" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-    </row>
-    <row r="2" spans="1:29" ht="23.25" customHeight="1">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+    </row>
+    <row r="2" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5" t="s">
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5" t="s">
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5" t="s">
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5" t="s">
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-    </row>
-    <row r="3" spans="1:29" ht="23.25" customHeight="1">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+    </row>
+    <row r="3" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5" t="s">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5" t="s">
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5" t="s">
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5" t="s">
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5" t="s">
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-    </row>
-    <row r="4" spans="1:29" ht="23.25" customHeight="1">
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+    </row>
+    <row r="4" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1223,7 +1227,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="23.25" customHeight="1">
+    <row r="5" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1312,7 +1316,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="23.25" customHeight="1">
+    <row r="6" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -1401,124 +1405,124 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="23.25" customHeight="1">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="6" t="str">
+      <c r="B7" s="5" t="str">
         <f>$B$3&amp;"_"&amp;B6</f>
         <v>총지수_원자료</v>
       </c>
-      <c r="C7" s="6" t="str">
+      <c r="C7" s="5" t="str">
         <f t="shared" ref="C7:E7" si="0">$B$3&amp;"_"&amp;C6</f>
         <v>총지수_전기대비증감</v>
       </c>
-      <c r="D7" s="6" t="str">
+      <c r="D7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>총지수_전년동기대비증감</v>
       </c>
-      <c r="E7" s="6" t="str">
+      <c r="E7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>총지수_이동평균(3기간)</v>
       </c>
-      <c r="F7" s="6" t="str">
+      <c r="F7" s="5" t="str">
         <f>$F$3&amp;"_"&amp;F6</f>
         <v xml:space="preserve">    운송장비_원자료</v>
       </c>
-      <c r="G7" s="6" t="str">
+      <c r="G7" s="5" t="str">
         <f t="shared" ref="G7:I7" si="1">$F$3&amp;"_"&amp;G6</f>
         <v xml:space="preserve">    운송장비_전기대비증감</v>
       </c>
-      <c r="H7" s="6" t="str">
+      <c r="H7" s="5" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    운송장비_전년동기대비증감</v>
       </c>
-      <c r="I7" s="6" t="str">
+      <c r="I7" s="5" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    운송장비_이동평균(3기간)</v>
       </c>
-      <c r="J7" s="6" t="str">
+      <c r="J7" s="5" t="str">
         <f>$J$3&amp;"_"&amp;J6</f>
         <v xml:space="preserve">    개인운송장비 운영_원자료</v>
       </c>
-      <c r="K7" s="6" t="str">
+      <c r="K7" s="5" t="str">
         <f t="shared" ref="K7:M7" si="2">$J$3&amp;"_"&amp;K6</f>
         <v xml:space="preserve">    개인운송장비 운영_전기대비증감</v>
       </c>
-      <c r="L7" s="6" t="str">
+      <c r="L7" s="5" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    개인운송장비 운영_전년동기대비증감</v>
       </c>
-      <c r="M7" s="6" t="str">
+      <c r="M7" s="5" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    개인운송장비 운영_이동평균(3기간)</v>
       </c>
-      <c r="N7" s="6" t="str">
+      <c r="N7" s="5" t="str">
         <f>$N$3&amp;"_"&amp;N6</f>
         <v xml:space="preserve">      철도 여객수송_원자료</v>
       </c>
-      <c r="O7" s="6" t="str">
+      <c r="O7" s="5" t="str">
         <f t="shared" ref="O7:Q7" si="3">$N$3&amp;"_"&amp;O6</f>
         <v xml:space="preserve">      철도 여객수송_전기대비증감</v>
       </c>
-      <c r="P7" s="6" t="str">
+      <c r="P7" s="5" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">      철도 여객수송_전년동기대비증감</v>
       </c>
-      <c r="Q7" s="6" t="str">
+      <c r="Q7" s="5" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">      철도 여객수송_이동평균(3기간)</v>
       </c>
-      <c r="R7" s="6" t="str">
+      <c r="R7" s="5" t="str">
         <f>$R$3&amp;"_"&amp;R6</f>
         <v xml:space="preserve">      도로 여객수송_원자료</v>
       </c>
-      <c r="S7" s="6" t="str">
+      <c r="S7" s="5" t="str">
         <f t="shared" ref="S7:U7" si="4">$R$3&amp;"_"&amp;S6</f>
         <v xml:space="preserve">      도로 여객수송_전기대비증감</v>
       </c>
-      <c r="T7" s="6" t="str">
+      <c r="T7" s="5" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">      도로 여객수송_전년동기대비증감</v>
       </c>
-      <c r="U7" s="6" t="str">
+      <c r="U7" s="5" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">      도로 여객수송_이동평균(3기간)</v>
       </c>
-      <c r="V7" s="6" t="str">
+      <c r="V7" s="5" t="str">
         <f>$V$3&amp;"_"&amp;V6</f>
         <v xml:space="preserve">      항공 및 수상여객운송_원자료</v>
       </c>
-      <c r="W7" s="6" t="str">
+      <c r="W7" s="5" t="str">
         <f t="shared" ref="W7:Y7" si="5">$V$3&amp;"_"&amp;W6</f>
         <v xml:space="preserve">      항공 및 수상여객운송_전기대비증감</v>
       </c>
-      <c r="X7" s="6" t="str">
+      <c r="X7" s="5" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">      항공 및 수상여객운송_전년동기대비증감</v>
       </c>
-      <c r="Y7" s="6" t="str">
+      <c r="Y7" s="5" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">      항공 및 수상여객운송_이동평균(3기간)</v>
       </c>
-      <c r="Z7" s="6" t="str">
+      <c r="Z7" s="5" t="str">
         <f>$Z$3&amp;"_"&amp;Z6</f>
         <v xml:space="preserve">      기타 여객운송_원자료</v>
       </c>
-      <c r="AA7" s="6" t="str">
+      <c r="AA7" s="5" t="str">
         <f t="shared" ref="AA7:AC7" si="6">$Z$3&amp;"_"&amp;AA6</f>
         <v xml:space="preserve">      기타 여객운송_전기대비증감</v>
       </c>
-      <c r="AB7" s="6" t="str">
+      <c r="AB7" s="5" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">      기타 여객운송_전년동기대비증감</v>
       </c>
-      <c r="AC7" s="6" t="str">
+      <c r="AC7" s="5" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">      기타 여객운송_이동평균(3기간)</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="23.25" customHeight="1">
+    <row r="8" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
@@ -1607,7 +1611,7 @@
         <v>90.7</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="23.25" customHeight="1">
+    <row r="9" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -1696,7 +1700,7 @@
         <v>91.3</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="23.25" customHeight="1">
+    <row r="10" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
@@ -1785,7 +1789,7 @@
         <v>91.6</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="23.25" customHeight="1">
+    <row r="11" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -1874,7 +1878,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="23.25" customHeight="1">
+    <row r="12" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -1963,7 +1967,7 @@
         <v>91.4</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="23.25" customHeight="1">
+    <row r="13" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -2052,7 +2056,7 @@
         <v>91.4</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="23.25" customHeight="1">
+    <row r="14" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
@@ -2141,7 +2145,7 @@
         <v>91.4</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="23.25" customHeight="1">
+    <row r="15" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
@@ -2230,7 +2234,7 @@
         <v>91.6</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="23.25" customHeight="1">
+    <row r="16" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
@@ -2319,7 +2323,7 @@
         <v>91.7</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="23.25" customHeight="1">
+    <row r="17" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
@@ -2408,7 +2412,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="23.25" customHeight="1">
+    <row r="18" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>43</v>
       </c>
@@ -2497,7 +2501,7 @@
         <v>91.9</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="23.25" customHeight="1">
+    <row r="19" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>44</v>
       </c>
@@ -2586,7 +2590,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="23.25" customHeight="1">
+    <row r="20" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>45</v>
       </c>
@@ -2675,7 +2679,7 @@
         <v>92.6</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="23.25" customHeight="1">
+    <row r="21" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
@@ -2764,7 +2768,7 @@
         <v>93.2</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="23.25" customHeight="1">
+    <row r="22" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>47</v>
       </c>
@@ -2853,7 +2857,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="23.25" customHeight="1">
+    <row r="23" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>48</v>
       </c>
@@ -2942,7 +2946,7 @@
         <v>93.6</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="23.25" customHeight="1">
+    <row r="24" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>49</v>
       </c>
@@ -3031,7 +3035,7 @@
         <v>93.3</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="23.25" customHeight="1">
+    <row r="25" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>50</v>
       </c>
@@ -3120,7 +3124,7 @@
         <v>93.2</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="23.25" customHeight="1">
+    <row r="26" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
@@ -3209,7 +3213,7 @@
         <v>93.2</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="23.25" customHeight="1">
+    <row r="27" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
@@ -3298,7 +3302,7 @@
         <v>93.3</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="23.25" customHeight="1">
+    <row r="28" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
@@ -3387,7 +3391,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="23.25" customHeight="1">
+    <row r="29" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
@@ -3476,7 +3480,7 @@
         <v>93.7</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="23.25" customHeight="1">
+    <row r="30" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>55</v>
       </c>
@@ -3565,7 +3569,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="23.25" customHeight="1">
+    <row r="31" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>56</v>
       </c>
@@ -3654,7 +3658,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="23.25" customHeight="1">
+    <row r="32" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>57</v>
       </c>
@@ -3743,7 +3747,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="23.25" customHeight="1">
+    <row r="33" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>58</v>
       </c>
@@ -3832,7 +3836,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="23.25" customHeight="1">
+    <row r="34" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>59</v>
       </c>
@@ -3921,7 +3925,7 @@
         <v>94.6</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="23.25" customHeight="1">
+    <row r="35" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>60</v>
       </c>
@@ -4010,7 +4014,7 @@
         <v>94.4</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="23.25" customHeight="1">
+    <row r="36" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
@@ -4099,7 +4103,7 @@
         <v>94.3</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="23.25" customHeight="1">
+    <row r="37" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>62</v>
       </c>
@@ -4188,7 +4192,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="23.25" customHeight="1">
+    <row r="38" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>63</v>
       </c>
@@ -4277,7 +4281,7 @@
         <v>94.3</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="23.25" customHeight="1">
+    <row r="39" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>64</v>
       </c>
@@ -4366,7 +4370,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="23.25" customHeight="1">
+    <row r="40" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>65</v>
       </c>
@@ -4455,7 +4459,7 @@
         <v>94.6</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="23.25" customHeight="1">
+    <row r="41" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>66</v>
       </c>
@@ -4544,7 +4548,7 @@
         <v>94.6</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="23.25" customHeight="1">
+    <row r="42" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>67</v>
       </c>
@@ -4633,7 +4637,7 @@
         <v>94.6</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="23.25" customHeight="1">
+    <row r="43" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>68</v>
       </c>
@@ -4722,7 +4726,7 @@
         <v>94.9</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="23.25" customHeight="1">
+    <row r="44" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>69</v>
       </c>
@@ -4811,7 +4815,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="23.25" customHeight="1">
+    <row r="45" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>70</v>
       </c>
@@ -4900,7 +4904,7 @@
         <v>96.2</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="23.25" customHeight="1">
+    <row r="46" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>71</v>
       </c>
@@ -4989,7 +4993,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="23.25" customHeight="1">
+    <row r="47" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>72</v>
       </c>
@@ -5078,7 +5082,7 @@
         <v>96.3</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="23.25" customHeight="1">
+    <row r="48" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>73</v>
       </c>
@@ -5167,7 +5171,7 @@
         <v>96.2</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="23.25" customHeight="1">
+    <row r="49" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>74</v>
       </c>
@@ -5256,7 +5260,7 @@
         <v>96.1</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="23.25" customHeight="1">
+    <row r="50" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>75</v>
       </c>
@@ -5345,7 +5349,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="23.25" customHeight="1">
+    <row r="51" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>76</v>
       </c>
@@ -5434,7 +5438,7 @@
         <v>96.1</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="23.25" customHeight="1">
+    <row r="52" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>77</v>
       </c>
@@ -5523,7 +5527,7 @@
         <v>96.3</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="23.25" customHeight="1">
+    <row r="53" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>78</v>
       </c>
@@ -5612,7 +5616,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="23.25" customHeight="1">
+    <row r="54" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>79</v>
       </c>
@@ -5701,7 +5705,7 @@
         <v>96.8</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="23.25" customHeight="1">
+    <row r="55" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>80</v>
       </c>
@@ -5790,7 +5794,7 @@
         <v>97.2</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="23.25" customHeight="1">
+    <row r="56" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>81</v>
       </c>
@@ -5879,7 +5883,7 @@
         <v>97.7</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="23.25" customHeight="1">
+    <row r="57" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>82</v>
       </c>
@@ -5968,7 +5972,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="23.25" customHeight="1">
+    <row r="58" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>83</v>
       </c>
@@ -6057,7 +6061,7 @@
         <v>98.3</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="23.25" customHeight="1">
+    <row r="59" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>84</v>
       </c>
@@ -6146,7 +6150,7 @@
         <v>98.3</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="23.25" customHeight="1">
+    <row r="60" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>85</v>
       </c>
@@ -6235,7 +6239,7 @@
         <v>98.3</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="23.25" customHeight="1">
+    <row r="61" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>86</v>
       </c>
@@ -6324,7 +6328,7 @@
         <v>98.2</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="23.25" customHeight="1">
+    <row r="62" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>87</v>
       </c>
@@ -6413,7 +6417,7 @@
         <v>98.2</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="23.25" customHeight="1">
+    <row r="63" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>88</v>
       </c>
@@ -6502,7 +6506,7 @@
         <v>98.2</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="23.25" customHeight="1">
+    <row r="64" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>89</v>
       </c>
@@ -6591,7 +6595,7 @@
         <v>98.2</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="23.25" customHeight="1">
+    <row r="65" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>90</v>
       </c>
@@ -6680,7 +6684,7 @@
         <v>98.3</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="23.25" customHeight="1">
+    <row r="66" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>91</v>
       </c>
@@ -6769,7 +6773,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="23.25" customHeight="1">
+    <row r="67" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>92</v>
       </c>
@@ -6858,7 +6862,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="23.25" customHeight="1">
+    <row r="68" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>93</v>
       </c>
@@ -6947,7 +6951,7 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="23.25" customHeight="1">
+    <row r="69" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>94</v>
       </c>
@@ -7036,7 +7040,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="23.25" customHeight="1">
+    <row r="70" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>95</v>
       </c>
@@ -7125,7 +7129,7 @@
         <v>99.6</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="23.25" customHeight="1">
+    <row r="71" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>96</v>
       </c>
@@ -7214,7 +7218,7 @@
         <v>99.4</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="23.25" customHeight="1">
+    <row r="72" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>97</v>
       </c>
@@ -7303,7 +7307,7 @@
         <v>99.3</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="23.25" customHeight="1">
+    <row r="73" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>98</v>
       </c>
@@ -7392,7 +7396,7 @@
         <v>99.4</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="23.25" customHeight="1">
+    <row r="74" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>99</v>
       </c>
@@ -7481,7 +7485,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="23.25" customHeight="1">
+    <row r="75" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>100</v>
       </c>
@@ -7570,7 +7574,7 @@
         <v>99.8</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="23.25" customHeight="1">
+    <row r="76" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>101</v>
       </c>
@@ -7659,7 +7663,7 @@
         <v>100.4</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="23.25" customHeight="1">
+    <row r="77" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>102</v>
       </c>
@@ -7748,7 +7752,7 @@
         <v>100.9</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="23.25" customHeight="1">
+    <row r="78" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>103</v>
       </c>
@@ -7837,7 +7841,7 @@
         <v>101.4</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="23.25" customHeight="1">
+    <row r="79" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>104</v>
       </c>
@@ -7926,7 +7930,7 @@
         <v>101.7</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="23.25" customHeight="1">
+    <row r="80" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>105</v>
       </c>
@@ -8015,7 +8019,7 @@
         <v>102.3</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="23.25" customHeight="1">
+    <row r="81" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>106</v>
       </c>
@@ -8104,7 +8108,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="23.25" customHeight="1">
+    <row r="82" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>107</v>
       </c>
@@ -8193,7 +8197,7 @@
         <v>103.7</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="23.25" customHeight="1">
+    <row r="83" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>108</v>
       </c>
@@ -8282,7 +8286,7 @@
         <v>104.3</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="23.25" customHeight="1">
+    <row r="84" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>109</v>
       </c>
@@ -8371,7 +8375,7 @@
         <v>104.8</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="23.25" customHeight="1">
+    <row r="85" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>110</v>
       </c>
@@ -8460,7 +8464,7 @@
         <v>105.3</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="23.25" customHeight="1">
+    <row r="86" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>111</v>
       </c>
@@ -8549,7 +8553,7 @@
         <v>105.8</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="23.25" customHeight="1">
+    <row r="87" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>112</v>
       </c>
@@ -8638,7 +8642,7 @@
         <v>106.5</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="23.25" customHeight="1">
+    <row r="88" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>113</v>
       </c>
@@ -8727,7 +8731,7 @@
         <v>107.1</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="23.25" customHeight="1">
+    <row r="89" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>114</v>
       </c>
@@ -8816,7 +8820,7 @@
         <v>107.7</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="23.25" customHeight="1">
+    <row r="90" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>115</v>
       </c>
@@ -8905,7 +8909,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="23.25" customHeight="1">
+    <row r="91" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>116</v>
       </c>
@@ -8994,7 +8998,7 @@
         <v>108.8</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="23.25" customHeight="1">
+    <row r="92" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>117</v>
       </c>
@@ -9083,7 +9087,7 @@
         <v>109.7</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="23.25" customHeight="1">
+    <row r="93" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>118</v>
       </c>
@@ -9172,7 +9176,7 @@
         <v>110.3</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="23.25" customHeight="1">
+    <row r="94" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>119</v>
       </c>
@@ -9261,7 +9265,7 @@
         <v>110.7</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="23.25" customHeight="1">
+    <row r="95" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>120</v>
       </c>
@@ -9350,7 +9354,7 @@
         <v>110.9</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="23.25" customHeight="1">
+    <row r="96" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>121</v>
       </c>
@@ -9439,7 +9443,7 @@
         <v>111.5</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="23.25" customHeight="1">
+    <row r="97" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>122</v>
       </c>
@@ -9528,7 +9532,7 @@
         <v>112.1</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="23.25" customHeight="1">
+    <row r="98" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>123</v>
       </c>
@@ -9617,7 +9621,7 @@
         <v>112.6</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="23.25" customHeight="1">
+    <row r="99" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>124</v>
       </c>
@@ -9706,7 +9710,7 @@
         <v>112.8</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="23.25" customHeight="1">
+    <row r="100" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>125</v>
       </c>
@@ -9795,7 +9799,7 @@
         <v>112.9</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="23.25" customHeight="1">
+    <row r="101" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>126</v>
       </c>
@@ -9884,7 +9888,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="23.25" customHeight="1">
+    <row r="102" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>127</v>
       </c>
@@ -9973,7 +9977,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="23.25" customHeight="1">
+    <row r="103" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>128</v>
       </c>
@@ -10062,7 +10066,7 @@
         <v>113.1</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="23.25" customHeight="1">
+    <row r="104" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>129</v>
       </c>
@@ -10151,7 +10155,7 @@
         <v>113.4</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="23.25" customHeight="1">
+    <row r="105" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>130</v>
       </c>
@@ -10240,7 +10244,7 @@
         <v>113.8</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="23.25" customHeight="1">
+    <row r="106" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>131</v>
       </c>
@@ -10329,7 +10333,7 @@
         <v>114.3</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="23.25" customHeight="1">
+    <row r="107" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>132</v>
       </c>
@@ -10418,7 +10422,7 @@
         <v>114.6</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="23.25" customHeight="1">
+    <row r="108" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>133</v>
       </c>
@@ -10507,7 +10511,7 @@
         <v>114.8</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="23.25" customHeight="1">
+    <row r="109" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>134</v>
       </c>
@@ -10596,7 +10600,7 @@
         <v>114.9</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="23.25" customHeight="1">
+    <row r="110" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>135</v>
       </c>
@@ -10685,7 +10689,7 @@
         <v>115.1</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="23.25" customHeight="1">
+    <row r="111" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>136</v>
       </c>
@@ -10774,7 +10778,7 @@
         <v>115.2</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="23.25" customHeight="1">
+    <row r="112" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>137</v>
       </c>
@@ -10863,7 +10867,7 @@
         <v>115.3</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="23.25" customHeight="1">
+    <row r="113" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>138</v>
       </c>
@@ -10952,7 +10956,7 @@
         <v>115.4</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="23.25" customHeight="1">
+    <row r="114" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>139</v>
       </c>
@@ -11041,7 +11045,7 @@
         <v>115.4</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="23.25" customHeight="1">
+    <row r="115" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>140</v>
       </c>
@@ -11130,7 +11134,7 @@
         <v>115.8</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="23.25" customHeight="1">
+    <row r="116" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>141</v>
       </c>
@@ -11219,7 +11223,7 @@
         <v>116.4</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="23.25" customHeight="1">
+    <row r="117" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>142</v>
       </c>
@@ -11308,7 +11312,7 @@
         <v>116.9</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="23.25" customHeight="1">
+    <row r="118" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>143</v>
       </c>
@@ -11397,994 +11401,987 @@
         <v>117.2</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="23.25" customHeight="1">
+    <row r="119" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B119" s="3">
-        <v>114.01</v>
+        <v>0</v>
       </c>
       <c r="C119" s="3">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="D119" s="3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="E119" s="3">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F119" s="3">
-        <v>109.31</v>
+        <v>0</v>
       </c>
       <c r="G119" s="3">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="H119" s="3">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I119" s="3">
-        <v>109.1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="3">
-        <v>119.39</v>
+        <v>0</v>
       </c>
       <c r="K119" s="3">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="L119" s="3">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="M119" s="3">
-        <v>119.3</v>
+        <v>0</v>
       </c>
       <c r="N119" s="3">
-        <v>106.14</v>
+        <v>0</v>
       </c>
       <c r="O119" s="3">
         <v>0</v>
       </c>
       <c r="P119" s="3">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="Q119" s="3">
-        <v>106.4</v>
+        <v>0</v>
       </c>
       <c r="R119" s="3">
-        <v>114.78</v>
+        <v>0</v>
       </c>
       <c r="S119" s="3">
         <v>0</v>
       </c>
       <c r="T119" s="3">
-        <v>11.82</v>
+        <v>0</v>
       </c>
       <c r="U119" s="3">
-        <v>114.8</v>
+        <v>0</v>
       </c>
       <c r="V119" s="3">
-        <v>116.01</v>
+        <v>0</v>
       </c>
       <c r="W119" s="3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X119" s="3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y119" s="3">
-        <v>115.7</v>
+        <v>0</v>
       </c>
       <c r="Z119" s="3">
-        <v>117.2</v>
+        <v>0</v>
       </c>
       <c r="AA119" s="3">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="AB119" s="3">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC119" s="3">
-        <v>117.2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B120" s="3">
-        <v>114.1</v>
+        <v>0</v>
       </c>
       <c r="C120" s="3">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="D120" s="3">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="E120" s="3">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F120" s="3">
-        <v>109.21</v>
+        <v>0</v>
       </c>
       <c r="G120" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="3">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I120" s="3">
-        <v>109.2</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3">
-        <v>120.79</v>
+        <v>0</v>
       </c>
       <c r="K120" s="3">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="L120" s="3">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M120" s="3">
-        <v>119.1</v>
+        <v>0</v>
       </c>
       <c r="N120" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O120" s="3">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="P120" s="3">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="3">
-        <v>106.6</v>
+        <v>0</v>
       </c>
       <c r="R120" s="3">
-        <v>114.78</v>
+        <v>0</v>
       </c>
       <c r="S120" s="3">
         <v>0</v>
       </c>
       <c r="T120" s="3">
-        <v>11.82</v>
+        <v>0</v>
       </c>
       <c r="U120" s="3">
-        <v>114.8</v>
+        <v>0</v>
       </c>
       <c r="V120" s="3">
-        <v>116.43</v>
+        <v>0</v>
       </c>
       <c r="W120" s="3">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="X120" s="3">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y120" s="3">
-        <v>116.6</v>
+        <v>0</v>
       </c>
       <c r="Z120" s="3">
-        <v>117.33</v>
+        <v>0</v>
       </c>
       <c r="AA120" s="3">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AB120" s="3">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC120" s="3">
-        <v>117.3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B121" s="3">
-        <v>113.84</v>
+        <v>0</v>
       </c>
       <c r="C121" s="3">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="D121" s="3">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="E121" s="3">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F121" s="3">
-        <v>109.15</v>
+        <v>0</v>
       </c>
       <c r="G121" s="3">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="H121" s="3">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="I121" s="3">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="J121" s="3">
-        <v>117.26</v>
+        <v>0</v>
       </c>
       <c r="K121" s="3">
-        <v>-3.53</v>
+        <v>0</v>
       </c>
       <c r="L121" s="3">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M121" s="3">
-        <v>119.8</v>
+        <v>0</v>
       </c>
       <c r="N121" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O121" s="3">
         <v>0</v>
       </c>
       <c r="P121" s="3">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q121" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R121" s="3">
-        <v>114.78</v>
+        <v>0</v>
       </c>
       <c r="S121" s="3">
         <v>0</v>
       </c>
       <c r="T121" s="3">
-        <v>11.06</v>
+        <v>0</v>
       </c>
       <c r="U121" s="3">
-        <v>114.8</v>
+        <v>0</v>
       </c>
       <c r="V121" s="3">
-        <v>117.29</v>
+        <v>0</v>
       </c>
       <c r="W121" s="3">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="X121" s="3">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Y121" s="3">
-        <v>117.8</v>
+        <v>0</v>
       </c>
       <c r="Z121" s="3">
-        <v>117.41</v>
+        <v>0</v>
       </c>
       <c r="AA121" s="3">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AB121" s="3">
-        <v>2.5299999999999998</v>
+        <v>0</v>
       </c>
       <c r="AC121" s="3">
-        <v>117.4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B122" s="3">
-        <v>114.13</v>
+        <v>0</v>
       </c>
       <c r="C122" s="3">
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="D122" s="3">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="E122" s="3">
-        <v>114.2</v>
+        <v>0</v>
       </c>
       <c r="F122" s="3">
-        <v>108.52</v>
+        <v>0</v>
       </c>
       <c r="G122" s="3">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="H122" s="3">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="I122" s="3">
-        <v>108.7</v>
+        <v>0</v>
       </c>
       <c r="J122" s="3">
-        <v>121.47</v>
+        <v>0</v>
       </c>
       <c r="K122" s="3">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="L122" s="3">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="M122" s="3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="N122" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O122" s="3">
         <v>0</v>
       </c>
       <c r="P122" s="3">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q122" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R122" s="3">
-        <v>114.78</v>
+        <v>0</v>
       </c>
       <c r="S122" s="3">
         <v>0</v>
       </c>
       <c r="T122" s="3">
-        <v>8.14</v>
+        <v>0</v>
       </c>
       <c r="U122" s="3">
-        <v>114.8</v>
+        <v>0</v>
       </c>
       <c r="V122" s="3">
-        <v>119.62</v>
+        <v>0</v>
       </c>
       <c r="W122" s="3">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="X122" s="3">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y122" s="3">
-        <v>120.9</v>
+        <v>0</v>
       </c>
       <c r="Z122" s="3">
-        <v>117.49</v>
+        <v>0</v>
       </c>
       <c r="AA122" s="3">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AB122" s="3">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC122" s="3">
-        <v>117.5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B123" s="3">
-        <v>114.54</v>
+        <v>0</v>
       </c>
       <c r="C123" s="3">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="D123" s="3">
-        <v>2.2599999999999998</v>
+        <v>0</v>
       </c>
       <c r="E123" s="3">
-        <v>114.4</v>
+        <v>0</v>
       </c>
       <c r="F123" s="3">
-        <v>108.46</v>
+        <v>0</v>
       </c>
       <c r="G123" s="3">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="H123" s="3">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="I123" s="3">
-        <v>108.6</v>
+        <v>0</v>
       </c>
       <c r="J123" s="3">
-        <v>121.37</v>
+        <v>0</v>
       </c>
       <c r="K123" s="3">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="3">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M123" s="3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="N123" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O123" s="3">
         <v>0</v>
       </c>
       <c r="P123" s="3">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R123" s="3">
-        <v>114.93</v>
+        <v>0</v>
       </c>
       <c r="S123" s="3">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="T123" s="3">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U123" s="3">
-        <v>114.9</v>
+        <v>0</v>
       </c>
       <c r="V123" s="3">
-        <v>125.93</v>
+        <v>0</v>
       </c>
       <c r="W123" s="3">
-        <v>6.31</v>
+        <v>0</v>
       </c>
       <c r="X123" s="3">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="Y123" s="3">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="Z123" s="3">
-        <v>117.55</v>
+        <v>0</v>
       </c>
       <c r="AA123" s="3">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AB123" s="3">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC123" s="3">
-        <v>117.6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B124" s="3">
-        <v>114.65</v>
+        <v>0</v>
       </c>
       <c r="C124" s="3">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="D124" s="3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E124" s="3">
-        <v>114.6</v>
+        <v>0</v>
       </c>
       <c r="F124" s="3">
-        <v>108.75</v>
+        <v>0</v>
       </c>
       <c r="G124" s="3">
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="H124" s="3">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="I124" s="3">
-        <v>108.4</v>
+        <v>0</v>
       </c>
       <c r="J124" s="3">
-        <v>117.21</v>
+        <v>0</v>
       </c>
       <c r="K124" s="3">
-        <v>-4.16</v>
+        <v>0</v>
       </c>
       <c r="L124" s="3">
-        <v>-6.12</v>
+        <v>0</v>
       </c>
       <c r="M124" s="3">
-        <v>117.9</v>
+        <v>0</v>
       </c>
       <c r="N124" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O124" s="3">
         <v>0</v>
       </c>
       <c r="P124" s="3">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R124" s="3">
-        <v>114.91</v>
+        <v>0</v>
       </c>
       <c r="S124" s="3">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="T124" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U124" s="3">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="V124" s="3">
-        <v>117.58</v>
+        <v>0</v>
       </c>
       <c r="W124" s="3">
-        <v>-8.35</v>
+        <v>0</v>
       </c>
       <c r="X124" s="3">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Y124" s="3">
-        <v>119.5</v>
+        <v>0</v>
       </c>
       <c r="Z124" s="3">
-        <v>117.84</v>
+        <v>0</v>
       </c>
       <c r="AA124" s="3">
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="AB124" s="3">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC124" s="3">
-        <v>118.1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>150</v>
       </c>
       <c r="B125" s="3">
-        <v>114.69</v>
+        <v>0</v>
       </c>
       <c r="C125" s="3">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D125" s="3">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="E125" s="3">
-        <v>114.6</v>
+        <v>0</v>
       </c>
       <c r="F125" s="3">
-        <v>107.96</v>
+        <v>0</v>
       </c>
       <c r="G125" s="3">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="H125" s="3">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="I125" s="3">
-        <v>108.7</v>
+        <v>0</v>
       </c>
       <c r="J125" s="3">
-        <v>115.02</v>
+        <v>0</v>
       </c>
       <c r="K125" s="3">
-        <v>-2.19</v>
+        <v>0</v>
       </c>
       <c r="L125" s="3">
-        <v>-9.6999999999999993</v>
+        <v>0</v>
       </c>
       <c r="M125" s="3">
-        <v>116.3</v>
+        <v>0</v>
       </c>
       <c r="N125" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O125" s="3">
         <v>0</v>
       </c>
       <c r="P125" s="3">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q125" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R125" s="3">
-        <v>115.1</v>
+        <v>0</v>
       </c>
       <c r="S125" s="3">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="T125" s="3">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="U125" s="3">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="V125" s="3">
-        <v>115.12</v>
+        <v>0</v>
       </c>
       <c r="W125" s="3">
-        <v>-2.46</v>
+        <v>0</v>
       </c>
       <c r="X125" s="3">
-        <v>-5.59</v>
+        <v>0</v>
       </c>
       <c r="Y125" s="3">
-        <v>114.9</v>
+        <v>0</v>
       </c>
       <c r="Z125" s="3">
-        <v>118.84</v>
+        <v>0</v>
       </c>
       <c r="AA125" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB125" s="3">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AC125" s="3">
-        <v>118.7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B126" s="3">
-        <v>114.4</v>
+        <v>0</v>
       </c>
       <c r="C126" s="3">
-        <v>-0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="D126" s="3">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="E126" s="3">
-        <v>114.7</v>
+        <v>0</v>
       </c>
       <c r="F126" s="3">
-        <v>109.34</v>
+        <v>0</v>
       </c>
       <c r="G126" s="3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="H126" s="3">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="I126" s="3">
-        <v>108.5</v>
+        <v>0</v>
       </c>
       <c r="J126" s="3">
-        <v>116.71</v>
+        <v>0</v>
       </c>
       <c r="K126" s="3">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="L126" s="3">
-        <v>-4.05</v>
+        <v>0</v>
       </c>
       <c r="M126" s="3">
-        <v>116.7</v>
+        <v>0</v>
       </c>
       <c r="N126" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O126" s="3">
         <v>0</v>
       </c>
       <c r="P126" s="3">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q126" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R126" s="3">
-        <v>115.1</v>
+        <v>0</v>
       </c>
       <c r="S126" s="3">
         <v>0</v>
       </c>
       <c r="T126" s="3">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="U126" s="3">
-        <v>115.2</v>
+        <v>0</v>
       </c>
       <c r="V126" s="3">
-        <v>112.02</v>
+        <v>0</v>
       </c>
       <c r="W126" s="3">
-        <v>-3.1</v>
+        <v>0</v>
       </c>
       <c r="X126" s="3">
-        <v>-6.24</v>
+        <v>0</v>
       </c>
       <c r="Y126" s="3">
-        <v>114.1</v>
+        <v>0</v>
       </c>
       <c r="Z126" s="3">
-        <v>119.4</v>
+        <v>0</v>
       </c>
       <c r="AA126" s="3">
-        <v>0.56000000000000005</v>
+        <v>0</v>
       </c>
       <c r="AB126" s="3">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AC126" s="3">
-        <v>119.3</v>
-      </c>
-    </row>
-    <row r="127" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B127" s="3">
-        <v>114.91</v>
+        <v>0</v>
       </c>
       <c r="C127" s="3">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="D127" s="3">
-        <v>2.1800000000000002</v>
+        <v>0</v>
       </c>
       <c r="E127" s="3">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F127" s="3">
-        <v>108.24</v>
+        <v>0</v>
       </c>
       <c r="G127" s="3">
-        <v>-1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="H127" s="3">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="I127" s="3">
-        <v>108.4</v>
+        <v>0</v>
       </c>
       <c r="J127" s="3">
-        <v>118.3</v>
+        <v>0</v>
       </c>
       <c r="K127" s="3">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="L127" s="3">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M127" s="3">
-        <v>118.7</v>
+        <v>0</v>
       </c>
       <c r="N127" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O127" s="3">
         <v>0</v>
       </c>
       <c r="P127" s="3">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q127" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R127" s="3">
-        <v>115.37</v>
+        <v>0</v>
       </c>
       <c r="S127" s="3">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="T127" s="3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U127" s="3">
-        <v>115.3</v>
+        <v>0</v>
       </c>
       <c r="V127" s="3">
-        <v>115.21</v>
+        <v>0</v>
       </c>
       <c r="W127" s="3">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="X127" s="3">
-        <v>-3.51</v>
+        <v>0</v>
       </c>
       <c r="Y127" s="3">
-        <v>115.4</v>
+        <v>0</v>
       </c>
       <c r="Z127" s="3">
-        <v>119.68</v>
+        <v>0</v>
       </c>
       <c r="AA127" s="3">
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="AB127" s="3">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="AC127" s="3">
-        <v>119.8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>153</v>
       </c>
       <c r="B128" s="3">
-        <v>115.71</v>
+        <v>0</v>
       </c>
       <c r="C128" s="3">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D128" s="3">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="E128" s="3">
-        <v>115.6</v>
+        <v>0</v>
       </c>
       <c r="F128" s="3">
-        <v>107.49</v>
+        <v>0</v>
       </c>
       <c r="G128" s="3">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="H128" s="3">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="I128" s="3">
-        <v>107.8</v>
+        <v>0</v>
       </c>
       <c r="J128" s="3">
-        <v>121.06</v>
+        <v>0</v>
       </c>
       <c r="K128" s="3">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="L128" s="3">
-        <v>6.74</v>
+        <v>0</v>
       </c>
       <c r="M128" s="3">
-        <v>120.5</v>
+        <v>0</v>
       </c>
       <c r="N128" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O128" s="3">
         <v>0</v>
       </c>
       <c r="P128" s="3">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="Q128" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R128" s="3">
-        <v>115.31</v>
+        <v>0</v>
       </c>
       <c r="S128" s="3">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="T128" s="3">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="U128" s="3">
-        <v>115.3</v>
+        <v>0</v>
       </c>
       <c r="V128" s="3">
-        <v>119.1</v>
+        <v>0</v>
       </c>
       <c r="W128" s="3">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="X128" s="3">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="Y128" s="3">
-        <v>117.1</v>
+        <v>0</v>
       </c>
       <c r="Z128" s="3">
-        <v>120.18</v>
+        <v>0</v>
       </c>
       <c r="AA128" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB128" s="3">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AC128" s="3">
-        <v>120.2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:29" ht="23.25" customHeight="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B129" s="3">
-        <v>116.08</v>
+        <v>0</v>
       </c>
       <c r="C129" s="3">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="D129" s="3">
-        <v>2.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="E129" s="3">
-        <v>115.9</v>
+        <v>0</v>
       </c>
       <c r="F129" s="3">
-        <v>107.75</v>
+        <v>0</v>
       </c>
       <c r="G129" s="3">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="H129" s="3">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="I129" s="3">
-        <v>107.6</v>
+        <v>0</v>
       </c>
       <c r="J129" s="3">
-        <v>122.22</v>
+        <v>0</v>
       </c>
       <c r="K129" s="3">
-        <v>1.1599999999999999</v>
+        <v>0</v>
       </c>
       <c r="L129" s="3">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="M129" s="3">
-        <v>121.6</v>
+        <v>0</v>
       </c>
       <c r="N129" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="O129" s="3">
         <v>0</v>
       </c>
       <c r="P129" s="3">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="Q129" s="3">
-        <v>106.9</v>
+        <v>0</v>
       </c>
       <c r="R129" s="3">
-        <v>115.23</v>
+        <v>0</v>
       </c>
       <c r="S129" s="3">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="T129" s="3">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="U129" s="3">
-        <v>115.3</v>
+        <v>0</v>
       </c>
       <c r="V129" s="3">
-        <v>116.86</v>
+        <v>0</v>
       </c>
       <c r="W129" s="3">
-        <v>-2.2400000000000002</v>
+        <v>0</v>
       </c>
       <c r="X129" s="3">
-        <v>-2.25</v>
+        <v>0</v>
       </c>
       <c r="Y129" s="3">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="Z129" s="3">
-        <v>120.79</v>
+        <v>0</v>
       </c>
       <c r="AA129" s="3">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="AB129" s="3">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AC129" s="3">
-        <v>120.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:U3"/>
     <mergeCell ref="B1:AC1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:I2"/>
@@ -12393,6 +12390,13 @@
     <mergeCell ref="R2:U2"/>
     <mergeCell ref="V2:Y2"/>
     <mergeCell ref="Z2:AC2"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="R3:U3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12402,121 +12406,121 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="196"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" customHeight="1">
+    <row r="1" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="23.25" customHeight="1">
+    <row r="2" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="23.25" customHeight="1">
+    <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="23.25" customHeight="1">
+    <row r="4" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+    <row r="5" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="23.25" customHeight="1">
+    <row r="6" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="23.25" customHeight="1">
+    <row r="7" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" ht="23.25" customHeight="1">
+    <row r="8" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:1" ht="23.25" customHeight="1">
+    <row r="9" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="23.25" customHeight="1">
+    <row r="10" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="23.25" customHeight="1">
+    <row r="11" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="23.25" customHeight="1">
+    <row r="12" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="23.25" customHeight="1">
+    <row r="13" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="23.25" customHeight="1">
+    <row r="14" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="23.25" customHeight="1">
+    <row r="15" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="23.25" customHeight="1">
+    <row r="16" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="23.25" customHeight="1">
+    <row r="17" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="23.25" customHeight="1">
+    <row r="18" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="23.25" customHeight="1">
+    <row r="19" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="23.25" customHeight="1">
+    <row r="20" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1" ht="23.25" customHeight="1">
+    <row r="21" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="23.25" customHeight="1">
+    <row r="22" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="23.25" customHeight="1">
+    <row r="23" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="23.25" customHeight="1">
+    <row r="24" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
     </row>
   </sheetData>
